--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541AB346-09B6-48C4-89D9-5434F9578829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4FBC01-1B33-41C0-A4AC-79EF8235D1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>번호</t>
   </si>
@@ -95,6 +95,21 @@
   </si>
   <si>
     <t>서지영</t>
+  </si>
+  <si>
+    <t>김양우</t>
+  </si>
+  <si>
+    <t>양현철</t>
+  </si>
+  <si>
+    <t>박종운</t>
+  </si>
+  <si>
+    <t>종운동생</t>
+  </si>
+  <si>
+    <t>민규</t>
   </si>
 </sst>
 </file>
@@ -466,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -707,6 +722,46 @@
         <v>1</v>
       </c>
     </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4FBC01-1B33-41C0-A4AC-79EF8235D1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610C26BD-B7B4-4DB5-85E8-B829710FB80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>번호</t>
   </si>
@@ -97,19 +97,28 @@
     <t>서지영</t>
   </si>
   <si>
-    <t>김양우</t>
-  </si>
-  <si>
-    <t>양현철</t>
-  </si>
-  <si>
-    <t>박종운</t>
-  </si>
-  <si>
-    <t>종운동생</t>
-  </si>
-  <si>
-    <t>민규</t>
+    <t>남1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -481,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -762,6 +771,14 @@
         <v>29</v>
       </c>
     </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610C26BD-B7B4-4DB5-85E8-B829710FB80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA4D6A7-6DC6-452A-B0DA-B90CBFD134E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="465" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -520,7 +520,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -531,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -542,7 +542,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -553,10 +553,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -564,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -575,7 +572,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -586,7 +583,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,7 +594,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -605,7 +605,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -616,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -627,7 +627,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -635,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -646,10 +649,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -676,7 +676,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -684,7 +687,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -695,7 +698,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -706,7 +709,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -714,7 +717,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -725,10 +728,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -780,6 +780,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C29">
+    <sortCondition ref="B1:B29"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA4D6A7-6DC6-452A-B0DA-B90CBFD134E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55712EBE-A07E-4636-A18E-7C20447B4EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="465" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>한지윤</t>
   </si>
   <si>
-    <t>카밀라</t>
-  </si>
-  <si>
     <t>정준섭</t>
   </si>
   <si>
@@ -118,6 +115,10 @@
   </si>
   <si>
     <t>여3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>까밀라</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -509,7 +510,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -520,7 +521,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -553,7 +554,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -561,7 +562,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -594,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -605,7 +606,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -627,7 +628,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -649,7 +650,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -657,7 +658,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -665,7 +666,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -687,7 +688,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -698,7 +699,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -709,7 +710,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -717,7 +718,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -736,7 +737,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -744,7 +745,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -752,7 +753,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -760,7 +761,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -768,7 +769,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -776,7 +777,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55712EBE-A07E-4636-A18E-7C20447B4EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9160172-C716-411A-A193-46E196FC569D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1185" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>번호</t>
   </si>
@@ -92,34 +92,46 @@
   </si>
   <si>
     <t>서지영</t>
-  </si>
-  <si>
-    <t>남1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>까밀라</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남1.1</t>
+  </si>
+  <si>
+    <t>남1.2</t>
+  </si>
+  <si>
+    <t>남2.1</t>
+  </si>
+  <si>
+    <t>남2.2</t>
+  </si>
+  <si>
+    <t>남3.1</t>
+  </si>
+  <si>
+    <t>남3.2</t>
+  </si>
+  <si>
+    <t>여1.1</t>
+  </si>
+  <si>
+    <t>여1.2</t>
+  </si>
+  <si>
+    <t>여2.1</t>
+  </si>
+  <si>
+    <t>여2.2</t>
+  </si>
+  <si>
+    <t>여3.1</t>
+  </si>
+  <si>
+    <t>여3.2</t>
   </si>
 </sst>
 </file>
@@ -491,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -718,7 +730,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -737,7 +749,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -745,7 +757,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -753,7 +765,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -761,7 +773,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -769,7 +781,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -777,7 +789,55 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9160172-C716-411A-A193-46E196FC569D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A257C7-2492-4966-83B1-0565A0BCFB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9000" yWindow="1485" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,40 +98,41 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>남1.1</t>
-  </si>
-  <si>
     <t>남1.2</t>
   </si>
   <si>
-    <t>남2.1</t>
-  </si>
-  <si>
-    <t>남2.2</t>
-  </si>
-  <si>
     <t>남3.1</t>
   </si>
   <si>
     <t>남3.2</t>
   </si>
   <si>
-    <t>여1.1</t>
-  </si>
-  <si>
     <t>여1.2</t>
   </si>
   <si>
-    <t>여2.1</t>
-  </si>
-  <si>
     <t>여2.2</t>
   </si>
   <si>
-    <t>여3.1</t>
-  </si>
-  <si>
     <t>여3.2</t>
+  </si>
+  <si>
+    <t>최지원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이휘영</t>
+  </si>
+  <si>
+    <t>까미게스트</t>
+  </si>
+  <si>
+    <t>수현남편님</t>
+  </si>
+  <si>
+    <t>박수현</t>
+  </si>
+  <si>
+    <t>김예진</t>
   </si>
 </sst>
 </file>
@@ -749,7 +750,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -757,7 +758,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -765,7 +766,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -773,7 +774,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -781,7 +782,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -789,7 +790,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -797,7 +798,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,7 +806,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -813,7 +814,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -821,7 +822,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -829,7 +830,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -837,7 +838,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A257C7-2492-4966-83B1-0565A0BCFB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE290A3-A517-4DB5-9F60-64DAF969FD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="1485" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>번호</t>
   </si>
@@ -96,43 +96,6 @@
   <si>
     <t>까밀라</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남1.2</t>
-  </si>
-  <si>
-    <t>남3.1</t>
-  </si>
-  <si>
-    <t>남3.2</t>
-  </si>
-  <si>
-    <t>여1.2</t>
-  </si>
-  <si>
-    <t>여2.2</t>
-  </si>
-  <si>
-    <t>여3.2</t>
-  </si>
-  <si>
-    <t>최지원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이휘영</t>
-  </si>
-  <si>
-    <t>까미게스트</t>
-  </si>
-  <si>
-    <t>수현남편님</t>
-  </si>
-  <si>
-    <t>박수현</t>
-  </si>
-  <si>
-    <t>김예진</t>
   </si>
 </sst>
 </file>
@@ -504,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -743,102 +706,6 @@
       </c>
       <c r="B23" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/participation.xlsx
+++ b/dataset/participation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\matching\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE290A3-A517-4DB5-9F60-64DAF969FD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57ABC9DD-90B8-48E7-9AA2-51B49F6BBBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10690" yWindow="-15480" windowWidth="15270" windowHeight="10010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>번호</t>
   </si>
@@ -95,6 +95,14 @@
   </si>
   <si>
     <t>까밀라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박연규</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김예진</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -160,10 +168,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -510,9 +521,6 @@
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -551,9 +559,6 @@
       <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -636,6 +641,9 @@
       <c r="B16" t="s">
         <v>16</v>
       </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -644,9 +652,6 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -666,9 +671,6 @@
       <c r="B19" t="s">
         <v>11</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -677,9 +679,6 @@
       <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -688,6 +687,9 @@
       <c r="B21" t="s">
         <v>13</v>
       </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -706,6 +708,31 @@
       </c>
       <c r="B23" t="s">
         <v>10</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
